--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46191</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46177</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45793</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45723</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45791</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>45845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45082</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45785</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45895</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45429</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45786</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45797</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45884</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45709</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45978</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45786</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45797</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45800</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45371</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>45764</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45804</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45167</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45098</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45915</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45953</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45953</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44483</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>45208</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>46183</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>46092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45785</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45791</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45671</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45614</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>46148</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45561</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>46183</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45867</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>45866</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>46177</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45783</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>45786</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45131</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45812</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45812</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45835</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45837</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45751</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45183</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45188</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45762</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>45889</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45898</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45622</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>46148</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>45187</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45191</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>45967</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>45548</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45618</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>46101</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45106</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45866</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45859</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45867</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44830</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45142</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45614</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45777</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45785</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>45786</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45356</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44641</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45797</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45302</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45827</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45349</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45702</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45894</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44966</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45951</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45960</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45979</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>46013</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45751</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45624</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45112</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45442</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>46059</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45446</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>46072</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>46072</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>46072</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45579</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>46092</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>46095</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>44641</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>46244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>46205</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45411</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45119</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45785</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45785</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45789</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45789</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45791</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>45790</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45791</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45791</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45796</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45548</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>46282</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45826</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45837</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45837</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44557</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44833</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44813</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44868</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44789</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44782</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44524</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44557</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44607</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44491</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44879</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>44830</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44712</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44849</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44846</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44616</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44804</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44799</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44854</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44887</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44845</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44860</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44833</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44642</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44642</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44469</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44641</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>44790</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45610</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45187</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45474</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45261</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45125</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44728</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44629</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45351</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45058</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45058</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>44608</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44860</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45629</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>44469</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44578</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45636</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45645</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>44845</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45637</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45579</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>44615</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45735</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45029</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>44889</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>45434</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45545</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>44671</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>44566</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45460</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45246</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>44851</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45257</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45439</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>44977</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>45394</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>44494</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45544</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45518</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45453</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44526</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>45244</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45058</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45092</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45386</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45394</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>44872</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>44558</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>45764</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44826</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44826</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45334</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45520</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45201</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>44467</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45107</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>44732</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45244</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45884</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>44798</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>44721</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>44676</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45579</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45953</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45821</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45888</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45210</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45671</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45455</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45455</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45761</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45895</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>45589</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>45190</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45884</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45886</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>46024</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45898</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>45898</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>45903</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45927</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>46139</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>46093</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45904</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45918</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44952</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45907</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>44952</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45895</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>46066</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>45622</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>45058</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>45903</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>45614</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>46141</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45915</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>46094</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45915</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45915</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>45916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45916</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45182</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>45918</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44889</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>45940</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>46057</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45924</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45924</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>44615</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45579</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45930</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45930</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45762</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44522</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45922</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45932</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45590</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45761</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>46147</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45938</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>45058</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45939</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>46147</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45187</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45943</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>45541</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44846</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44854</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45951</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>45950</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45950</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45951</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45951</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45951</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45951</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44818</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45950</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45953</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>44529</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45952</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>45953</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45952</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45166</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45952</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45953</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45953</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45442</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>46150</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>46152</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45954</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45624</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>46150</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45580</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45965</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46029</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>45733</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45510</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44732</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>45163</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>44655</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44531</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>46029</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45558</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45042</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45469</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45975</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>44725</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45723</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45981</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45981</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45982</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>45985</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45985</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45985</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45624</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>46066</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44880</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45982</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>45092</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45231</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>46160</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>46160</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45586</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45182</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45621</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45915</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45188</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45953</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>46000</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45058</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>46006</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>46006</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>46007</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>46072</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45555</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>46150</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45182</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>46019</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>45972</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45985</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45985</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>46019</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>45916</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>46023</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>46024</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>46024</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>46027</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>46029</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45646</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45441</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>44557</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>46033</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>44893</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45435</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>46035</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46041</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46174</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46041</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>46171</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45032</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>46044</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>46049</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44575</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>46098</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45188</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>46051</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>46050</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>46050</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>45622</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>45058</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>45406</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>45593</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>46055</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>45043</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>46057</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46059</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>46057</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>46056</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>46056</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>46056</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45195</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45189</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46056</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>46056</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45562</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45175</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>46105</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>46066</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45250</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39069,7 +39069,7 @@
         <v>46066</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>46070</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45625</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45117</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45579</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>46182</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>46072</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>46072</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>46072</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>46072</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>46072</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>44869</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>46076</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>46077</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>46079</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>46079</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>46079</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>46079</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>46079</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>46083</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45435</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>46083</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>46084</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45446</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45386</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45103</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45553</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45579</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46091</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>46091</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>46092</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>46092</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>45579</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>46092</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>46091</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>46092</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>46095</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>46087</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>44952</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>46191</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>46191</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>46098</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>46195</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>46196</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>46105</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>46106</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44530</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>44531</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45079</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>44616</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>46106</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45614</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45495</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>46111</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45407</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>46114</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>45344</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>44630</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>46119</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>46202</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43680,7 +43680,7 @@
         <v>46126</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43753,7 +43753,7 @@
         <v>46202</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>46125</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>46202</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45861</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44050,7 +44050,7 @@
         <v>45579</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>44725</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45252</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>44869</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>44886</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>45656</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>46203</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>44798</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45370</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>44557</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>44839</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45148</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>46248</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>46205</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>46252</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>46253</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45495</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45250</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>46253</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>46253</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>45104</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>46252</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>44936</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>44595</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>46254</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>44872</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>46255</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46071,7 +46071,7 @@
         <v>46212</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
         <v>44924</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45595</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>46259</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>46259</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45749</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>46259</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>46106</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>45671</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>44888</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44530</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>46259</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>44952</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45209</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>45569</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44889</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45099</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>44895</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>45560</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>45987</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>45569</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45498</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>46252</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45033</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45782</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45783</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>46232</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46232</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>46275</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45784</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>46232</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>46232</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>46275</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>46232</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45784</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45785</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>46066</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45789</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>44721</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>46041</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45789</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>46188</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>45446</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45572</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
         <v>46281</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>45789</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49494,7 +49494,7 @@
         <v>45786</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>46280</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44915</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>46281</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45790</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>46281</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45793</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>44603</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>45258</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>46240</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         <v>45602</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>45699</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>46282</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>44874</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45798</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45429</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50692,7 +50692,7 @@
         <v>45511</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         <v>45805</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45811</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45580</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50994,7 +50994,7 @@
         <v>45819</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45818</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45819</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51228,7 +51228,7 @@
         <v>45824</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45822</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45822</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45827</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>45831</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51618,7 +51618,7 @@
         <v>45831</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45834</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45838</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45839</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>45839</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45837</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>45837</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52159,7 +52159,7 @@
         <v>45840</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52232,7 +52232,7 @@
         <v>45840</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52305,7 +52305,7 @@
         <v>45840</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52378,7 +52378,7 @@
         <v>45840</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52456,7 +52456,7 @@
         <v>45845</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45847</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45847</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>45849</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>45855</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>45859</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52904,7 +52904,7 @@
         <v>45859</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>45798</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>45859</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45859</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53196,7 +53196,7 @@
         <v>45877</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53269,7 +53269,7 @@
         <v>45880</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53342,7 +53342,7 @@
         <v>45880</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45883</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53488,7 +53488,7 @@
         <v>45114</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45394</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45041</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45394</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>45041</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>45036</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45733</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>45758</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>46083</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>46083</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>46098</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>46162</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>46162</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>

--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46191</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46177</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45845</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45723</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>45791</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45924</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45924</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45082</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45785</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45895</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>45429</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45786</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45884</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45797</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45800</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45709</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45786</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45804</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45764</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45371</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>45791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45915</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>46092</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45953</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45953</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44483</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45098</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>46183</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>45208</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>45167</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45785</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45791</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45131</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45866</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>45867</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45812</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45614</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45812</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45671</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45614</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>46148</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45835</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45837</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45329</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>46183</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>46205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>46177</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45561</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45783</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45786</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45106</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45302</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>45797</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45889</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>45898</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>45889</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>46101</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45867</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45859</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45866</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45618</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45142</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45762</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45187</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45827</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45751</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>46148</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45614</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>45622</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45188</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>45548</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45777</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>45786</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44641</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45785</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45356</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45702</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45548</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45796</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44966</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45894</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>45624</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>46072</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>46072</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>46072</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>46092</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45446</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>45951</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45960</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45979</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45826</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>46013</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>45837</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45837</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>46059</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>46095</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>46205</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>44641</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45751</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45112</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>46282</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>46244</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>45442</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45579</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45349</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45411</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45119</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45785</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45785</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>45790</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45789</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45789</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45791</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45791</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45791</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44557</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44833</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44813</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44868</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44789</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44782</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44524</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44557</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44607</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44491</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44879</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>44830</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44712</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44849</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44846</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44616</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44804</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44799</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44854</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44845</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44887</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44860</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44642</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44642</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44469</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44833</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44790</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>44641</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>44798</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45058</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45334</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45043</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45092</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45434</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>44952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45250</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44854</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>44467</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45545</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45793</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44603</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45446</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45699</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45884</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44839</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>46019</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45985</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45972</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>46019</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45985</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45916</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>46023</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>46024</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>46024</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>46027</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45435</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45518</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44531</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>45602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>44886</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45884</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45511</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44874</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45798</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45469</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45429</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>46029</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>45498</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45883</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>45821</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45888</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44869</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>46033</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>46035</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45886</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>44880</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45033</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45439</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44889</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45895</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44872</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46041</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>44897</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45898</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45898</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46044</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>44530</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>44531</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>46050</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>46049</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45904</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>46050</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45907</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>46051</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>46056</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>44889</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45406</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>46055</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>46056</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>46056</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>46056</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>46056</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45915</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>46057</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45915</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>46057</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45916</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45915</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45916</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45918</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>46066</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45555</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45544</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45351</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44557</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44888</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45182</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45924</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45624</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>46070</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45924</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>46072</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>46072</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46072</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>46072</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>46072</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45032</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>46076</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>46077</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>46079</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46079</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45930</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>46079</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46079</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46079</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45930</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>46083</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45922</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45932</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>46083</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45805</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>46084</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45580</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>44630</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45614</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45579</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46091</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>44893</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>45572</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>46091</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46091</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>46091</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>46091</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>46092</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45938</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>44676</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45560</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>46092</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>46092</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>46092</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45579</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45939</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>44977</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45943</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45386</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>46098</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45569</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45950</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45950</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>45182</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45950</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>46105</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>45951</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45951</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45553</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45951</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45951</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45951</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45952</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>45952</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>46106</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>46106</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45954</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45953</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45953</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45953</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>46111</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45953</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45811</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>46114</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45569</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>46119</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45579</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>45636</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46125</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45625</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45965</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>46126</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45971</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45642</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45818</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45975</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44469</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45610</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45861</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>44725</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>44522</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45981</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45981</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45104</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45982</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45985</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45985</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45210</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45637</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45985</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45455</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45982</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45723</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45953</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45614</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45761</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>46000</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45940</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45510</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>44851</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>44952</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46006</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>46006</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45819</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>46139</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45953</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>46007</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45819</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46066</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45764</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44845</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45622</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44846</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45822</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>46024</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45824</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>44529</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45755</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45822</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45927</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45589</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44798</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45586</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45079</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45918</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45624</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45175</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45903</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45058</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45895</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>46094</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>46057</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>46093</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>46141</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>44616</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>44860</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45590</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45761</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45163</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>44895</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45831</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>46147</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45735</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>46147</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38558,7 +38558,7 @@
         <v>46150</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>46150</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>44872</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>46029</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>46152</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45209</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45834</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45042</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46029</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44869</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45837</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39381,7 +39381,7 @@
         <v>45838</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45837</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>46160</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>46160</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45092</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>46066</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45840</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45840</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45840</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45394</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45839</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45103</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>45840</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45839</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45915</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>44526</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45845</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45344</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45656</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>46150</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45847</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>45847</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45849</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>46072</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>45257</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45855</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45107</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45859</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45798</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45859</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45859</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45859</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>46174</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>44558</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45455</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>44732</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45029</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>46098</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>46105</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>46059</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>45593</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45595</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>44494</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>45182</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>46182</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>45125</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>44575</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45460</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>45166</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>46087</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45580</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45558</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>46095</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>46191</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>46191</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>44557</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>46195</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45187</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45880</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45880</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>44578</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>46196</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>45877</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45148</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46202</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45579</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>46202</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>46202</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>46205</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45058</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45386</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>45646</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>46252</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44608</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>44615</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44966,7 +44966,7 @@
         <v>44615</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>46252</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>46253</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>46253</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46253</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>46254</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45117</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45495</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45231</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>44732</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>46255</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45441</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45862,7 +45862,7 @@
         <v>46212</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>46106</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>46259</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>46259</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45435</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>46259</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>44671</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>44721</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45244</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45749</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45987</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45671</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>46252</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45370</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44595</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>44826</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>44826</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45261</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>46275</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>46232</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>46232</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>45495</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45250</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>45541</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>46232</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>46275</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>46232</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>46232</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>46041</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46188</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>46280</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>46066</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>45244</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>46240</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>46281</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>46281</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>46282</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>46281</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45671</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45733</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48900,7 +48900,7 @@
         <v>45622</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>45520</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>44629</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>46286</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>44566</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>46288</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45099</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>46289</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>46289</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>46248</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>46259</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>46289</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>46289</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>45645</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>44530</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>44655</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45195</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45252</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45562</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>45442</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50395,7 +50395,7 @@
         <v>45762</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45579</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45187</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50624,7 +50624,7 @@
         <v>44952</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>45188</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>44936</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>44889</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>44728</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45188</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45394</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>45474</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51218,7 +51218,7 @@
         <v>44725</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45579</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45579</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45246</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45190</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45002</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45058</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45201</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45058</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>44924</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45625</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>44818</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45621</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45629</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45407</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>45058</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45058</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45782</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45783</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45784</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>45784</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45446</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44721</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45785</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45572</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45786</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45789</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53254,7 +53254,7 @@
         <v>45789</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53332,7 +53332,7 @@
         <v>45789</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45790</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>44915</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>45114</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45394</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>45041</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53785,7 +53785,7 @@
         <v>45394</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53863,7 +53863,7 @@
         <v>45041</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45036</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45733</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>45758</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>46083</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>46083</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54326,7 +54326,7 @@
         <v>46098</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>46162</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54477,7 +54477,7 @@
         <v>46162</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>

--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46191</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46177</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45845</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45723</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>45791</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45924</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45924</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45082</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45785</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45895</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>45429</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45786</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45884</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45797</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45800</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45709</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45786</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45804</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45764</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45371</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>45791</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45915</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>46092</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45953</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45953</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44483</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45098</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>46183</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>45208</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>45167</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45785</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45791</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45131</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45866</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>45867</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45812</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45614</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45812</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45671</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45614</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>46148</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45835</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45837</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45329</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>46183</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>46205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>46177</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45561</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45783</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45786</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45106</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45302</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>45797</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45889</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>45898</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>45889</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>46101</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45867</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45859</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45866</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45618</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45142</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45762</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45187</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45827</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45751</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>46148</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45614</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>45622</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45188</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>45548</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45777</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>45786</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44641</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45785</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45356</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45702</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45548</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45796</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44966</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45894</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>45624</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>46072</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>46072</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>46072</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>46092</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45446</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>45951</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45960</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45979</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45826</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>46013</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>45837</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45837</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>46059</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>46095</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>46205</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>44641</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45751</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45112</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>46282</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>46244</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>45442</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45579</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45349</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45411</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45119</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45785</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45785</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>45790</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45789</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45789</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45791</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45791</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45791</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44557</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44833</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44813</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44868</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44789</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44782</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44524</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44557</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44607</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44491</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44879</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>44830</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44712</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44849</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44846</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44616</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44804</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44799</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44854</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44845</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44887</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44860</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44642</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44642</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44469</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44833</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44790</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>44641</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>44798</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45058</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45334</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45043</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45092</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45434</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>44952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45250</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44854</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>44467</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45545</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45793</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44603</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45446</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45699</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45884</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44839</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>46019</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45985</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45972</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>46019</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45985</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45916</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>46023</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>46024</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>46024</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>46027</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45435</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45518</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44531</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>45602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>44886</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45884</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45511</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44874</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45798</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45469</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45429</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>46029</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>45498</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45883</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>45821</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45888</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44869</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>46033</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>46035</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45886</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>44880</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45033</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45439</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44889</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45895</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44872</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46041</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>44897</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45898</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45898</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46044</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>44530</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>44531</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>46050</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>46049</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45904</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>46050</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45907</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>46051</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>46056</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>44889</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45406</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>46055</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>46056</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>46056</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>46056</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>46056</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45915</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>46057</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45915</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>46057</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45916</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45915</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45916</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45918</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>46066</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45555</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45544</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45351</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44557</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44888</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45182</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45924</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45624</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>46070</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45924</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>46072</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>46072</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46072</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>46072</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>46072</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45032</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>46076</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>46077</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>46079</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46079</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45930</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>46079</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46079</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46079</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45930</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>46083</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45922</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45932</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>46083</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45805</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>46084</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45580</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>44630</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45614</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45579</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46091</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>44893</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>45572</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>46091</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46091</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>46091</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>46091</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>46092</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45938</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>44676</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45560</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>46092</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>46092</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>46092</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45579</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45939</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>44977</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45943</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45386</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>46098</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45569</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45950</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45950</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>45182</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45950</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>46105</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>45951</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45951</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45553</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45951</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45951</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45951</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45952</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>45952</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>46106</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>46106</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45954</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45953</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45953</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45953</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>46111</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45953</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45811</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>46114</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45569</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>46119</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45579</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>45636</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46125</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45625</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45965</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>46126</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45971</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45642</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45818</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45975</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44469</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45610</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45861</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>44725</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>44522</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45981</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45981</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45104</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45982</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45985</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45985</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45210</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45637</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45985</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45455</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45982</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45723</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45953</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45614</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45761</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>46000</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45940</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45510</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>44851</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>44952</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46006</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>46006</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45819</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>46139</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45953</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>46007</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45819</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46066</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45764</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44845</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45622</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44846</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45822</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>46024</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45824</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>44529</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45755</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45822</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45927</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45589</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44798</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45586</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45079</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45918</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45624</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45175</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45903</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45058</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45895</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>46094</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>46057</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>46093</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>46141</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>44616</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>44860</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45590</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45761</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45163</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>44895</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45831</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>46147</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45735</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>46147</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38558,7 +38558,7 @@
         <v>46150</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>46150</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>44872</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>46029</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>46152</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45209</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45834</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45042</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46029</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44869</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45837</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39381,7 +39381,7 @@
         <v>45838</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45837</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>46160</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>46160</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45092</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>46066</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45840</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45840</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45840</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45394</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45839</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45103</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>45840</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45839</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45915</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>44526</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45845</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45344</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45656</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>46150</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45847</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>45847</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45849</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>46072</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>45257</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45855</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45107</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45859</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45798</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45859</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45859</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45859</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>46174</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>44558</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45455</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>44732</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45029</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>46098</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>46105</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>46059</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>45593</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45595</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>44494</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>45182</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>46182</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>45125</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>44575</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45460</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>45166</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>46087</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45580</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45558</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>46095</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>46191</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>46191</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>44557</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>46195</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45187</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45880</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45880</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>44578</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>46196</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>45877</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45148</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46202</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45579</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>46202</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>46202</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>46205</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45058</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45386</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>45646</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>46252</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44608</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>44615</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44966,7 +44966,7 @@
         <v>44615</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>46252</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>46253</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>46253</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46253</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>46254</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45117</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45495</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45231</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>44732</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>46255</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45441</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45862,7 +45862,7 @@
         <v>46212</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>46106</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>46259</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>46259</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45435</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>46259</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>44671</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>44721</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45244</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45749</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45987</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45671</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>46252</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45370</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44595</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>44826</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>44826</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45261</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>46275</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>46232</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>46232</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>45495</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45250</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>45541</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>46232</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>46275</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>46232</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>46232</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>46041</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46188</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>46280</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>46066</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>45244</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>46240</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>46281</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>46281</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>46282</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>46281</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45671</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45733</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48900,7 +48900,7 @@
         <v>45622</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>45520</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>44629</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>46286</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>44566</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>46288</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45099</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>46289</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>46289</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>46248</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>46259</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>46289</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>46289</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>45645</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>44530</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>44655</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45195</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45252</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45562</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>45442</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50395,7 +50395,7 @@
         <v>45762</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45579</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45187</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50624,7 +50624,7 @@
         <v>44952</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>45188</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>44936</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>44889</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>44728</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45188</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45394</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>45474</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51218,7 +51218,7 @@
         <v>44725</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45579</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45579</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45246</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45190</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45002</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45058</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45201</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45058</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>44924</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45625</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>44818</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45621</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45629</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45407</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>45058</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45058</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45782</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45783</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45784</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>45784</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45446</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44721</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45785</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45572</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45786</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45789</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53254,7 +53254,7 @@
         <v>45789</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53332,7 +53332,7 @@
         <v>45789</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45790</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>44915</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>45114</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45394</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>45041</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53785,7 +53785,7 @@
         <v>45394</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53863,7 +53863,7 @@
         <v>45041</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45036</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45733</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>45758</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>46083</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>46083</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54326,7 +54326,7 @@
         <v>46098</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>46162</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54477,7 +54477,7 @@
         <v>46162</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>

--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45789</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>46191</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46177</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45845</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45082</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45924</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45940</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45785</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45895</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>45429</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45786</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45786</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45797</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45800</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45884</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>45709</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45804</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45371</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>45764</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45167</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45791</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45915</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45953</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45953</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>45098</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45614</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44483</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45208</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>46183</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45785</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45786</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45131</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>45812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45812</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>45867</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45866</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>45614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45671</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45835</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45837</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>46148</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>46183</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45329</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>46205</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>46177</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45561</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45783</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45751</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45183</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45786</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45356</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44641</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>45967</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45898</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45797</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45302</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>45889</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45188</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46101</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45866</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>45867</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>45827</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45762</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45622</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>46148</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45187</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>45191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45548</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45618</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45106</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44830</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45142</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>45614</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45777</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45785</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45349</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45789</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45791</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45790</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45791</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>45791</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45894</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45796</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45548</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>46072</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>46072</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>46072</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45951</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45702</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45960</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>46092</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45979</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45826</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45837</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45837</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>46013</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45751</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45624</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>46059</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46095</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45112</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45442</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>46205</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45446</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45579</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46282</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44641</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45119</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45785</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45785</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45789</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44557</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44833</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44813</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44868</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44789</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44782</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44524</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44557</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44607</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44491</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44879</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>44830</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44712</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44849</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44846</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44616</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44804</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44799</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44854</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44887</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44845</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44860</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44642</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44642</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44833</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44641</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44790</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45610</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45187</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>44578</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45261</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45474</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45125</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44728</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45351</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44629</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>44860</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45629</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45789</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45058</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45058</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44608</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44845</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45446</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45572</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45789</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45786</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45636</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>45884</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>45886</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>46006</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45645</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>46006</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>44915</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>46007</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45002</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45790</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45637</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45821</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45888</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45579</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46019</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45735</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45972</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45985</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45985</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>46019</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45916</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>46023</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>46024</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>46024</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>46027</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44615</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45895</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45029</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>46029</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44889</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>46033</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45898</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45898</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>45793</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>46035</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45903</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>46041</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>46041</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>45904</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44671</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>45907</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45434</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45545</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>44897</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44603</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45258</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45602</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45915</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45699</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>46044</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45915</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45915</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44566</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44874</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45798</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45429</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45916</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45916</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45511</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>46051</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44851</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>46050</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45918</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45805</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>46050</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45460</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>45246</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>45257</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45625</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>46055</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45924</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45394</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>46057</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>45924</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>46057</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>46056</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>46056</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>44977</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>46056</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>46056</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44494</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45439</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45930</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45930</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45518</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45922</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45544</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45932</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45572</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>46070</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45938</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45939</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46072</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46072</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45244</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>44526</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>46072</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46072</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>46072</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>46076</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>46077</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45811</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45580</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>46079</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45058</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>46079</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45951</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>46079</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>46079</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45950</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45950</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>46079</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45951</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45951</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45951</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45951</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45950</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45953</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45952</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>46083</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>46083</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46084</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45953</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>45952</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45952</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45953</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45953</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44872</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45092</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45386</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45394</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45954</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44558</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45764</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44826</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>44826</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>46091</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>46092</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>46092</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45965</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>46091</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46091</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>46092</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>46091</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>46092</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45334</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>45971</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>46098</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>45755</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45201</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45520</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45975</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>46105</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>46106</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>45819</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45818</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45819</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>46106</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45981</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45107</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45982</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>45985</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45985</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>46111</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45824</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45822</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>46114</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45822</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44732</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45244</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45982</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>46119</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>44798</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45827</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>46126</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45953</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44721</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>44676</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45861</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45579</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46000</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45831</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>44725</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45210</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45671</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45455</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45455</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45834</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45838</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45839</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45839</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>45190</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>45837</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>45837</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>44798</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45840</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45840</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45840</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45840</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45845</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45847</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45847</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44952</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45849</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45953</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45182</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>44889</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45855</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45761</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45589</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>46024</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44615</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>45859</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45859</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45579</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45927</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>45798</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45859</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45859</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>46139</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>46093</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>45918</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>44952</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45762</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44522</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>46066</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45590</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45622</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45058</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45903</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45614</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>46141</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>46094</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45058</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45187</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45541</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44846</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44854</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45940</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>46057</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44818</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45761</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>44529</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>46147</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45166</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>46147</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45442</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
         <v>45624</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>46150</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>46152</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>45580</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>46150</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>46029</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45733</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45510</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>46029</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45042</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>44732</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45163</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44655</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>46066</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>44531</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45558</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         <v>46160</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>46160</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>45469</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>45915</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44725</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45723</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45877</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46072</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>46150</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>45880</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45880</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45624</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44880</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>46174</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45092</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45231</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45883</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>46098</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45884</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>46059</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45586</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>46105</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45182</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45621</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45188</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>46095</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>46087</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45058</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45555</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>46191</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>46191</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>46195</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>45182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>46196</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>46202</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46202</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>46202</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45646</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>45441</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>44557</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>44893</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45435</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>46205</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>46212</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>45032</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46259</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>46259</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>46259</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44575</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45188</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46106</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45622</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45058</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45406</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45593</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45043</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45195</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45189</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45987</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45562</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45175</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45250</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45625</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45117</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45579</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>44869</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45435</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>46232</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>46232</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>46275</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>46232</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>46232</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>46275</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>46232</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>46066</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>46041</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47191,7 +47191,7 @@
         <v>45446</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>46188</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>46281</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45386</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>46280</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45103</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45553</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>46281</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>46281</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45579</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45579</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>46240</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>46282</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>44952</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>44530</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>44531</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45079</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>44616</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>46286</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45614</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48691,7 +48691,7 @@
         <v>46289</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>46288</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>46289</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45495</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45407</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>46289</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49144,7 +49144,7 @@
         <v>45344</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>44630</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>46289</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>46248</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45579</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45252</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>46259</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>44869</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>44886</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>46252</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>45656</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>46252</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>46252</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>46295</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
         <v>46091</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45895</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45370</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50415,7 +50415,7 @@
         <v>44557</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>46253</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>46253</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50634,7 +50634,7 @@
         <v>46255</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>44839</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>46254</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>46253</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45148</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45495</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45250</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45104</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>44936</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>44595</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>44872</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>44924</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45595</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45749</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45671</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>44888</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>44530</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>44952</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45209</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>45569</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>44889</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52192,7 +52192,7 @@
         <v>45099</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>44895</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>45560</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45569</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45498</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45033</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45782</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>45783</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45784</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>45784</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45785</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>45789</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53113,7 +53113,7 @@
         <v>44721</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>45114</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>45394</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45041</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45394</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>45041</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>45036</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45733</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53722,7 +53722,7 @@
         <v>45758</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>46083</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>46083</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>46098</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54034,7 +54034,7 @@
         <v>46162</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>46162</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>

--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45789</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>46191</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45793</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46177</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45845</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>45723</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45082</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45924</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45940</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45785</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45895</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>45429</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45786</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45786</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45797</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45800</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45884</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>45709</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45804</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45371</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>45764</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45167</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45791</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45915</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45953</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45953</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>45098</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45614</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44483</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45208</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>46183</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45785</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45786</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45131</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>45812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45812</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>45867</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45866</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>45614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45671</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45835</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>45837</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>46148</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>46183</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45329</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>46205</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>46177</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45561</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45783</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45751</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45183</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45786</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45356</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44641</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>45967</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45898</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45797</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45302</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>45889</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45188</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>46101</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45866</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>45867</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>45827</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45762</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45622</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>46148</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45187</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>45191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45548</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45618</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45106</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44830</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45142</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>45614</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45777</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45785</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45349</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45789</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45791</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45790</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45791</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>45791</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45894</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45796</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45548</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>46072</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>46072</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>46072</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45951</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45702</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45960</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>46092</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45979</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45826</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45837</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45837</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>46013</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45751</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45624</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>46059</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46095</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45112</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45442</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>46205</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45446</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45579</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46282</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44641</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45119</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45785</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45785</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45789</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44557</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44833</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44813</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44868</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44789</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44782</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44524</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44557</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44607</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44491</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44879</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>44830</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44712</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44849</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44846</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44616</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44804</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44799</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44854</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44887</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44845</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44860</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44642</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44642</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44833</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44641</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44790</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45610</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45187</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>44578</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45261</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45474</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45125</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44728</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45351</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44629</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>44860</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45629</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45789</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45058</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45058</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44608</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44845</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45446</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45572</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45789</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45786</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45636</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>45884</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>45886</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>46006</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45645</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>46006</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>44915</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>46007</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45002</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45790</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45637</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45821</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45888</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45579</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46019</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45735</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45972</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45985</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45985</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>46019</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45916</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>46023</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>46024</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>46024</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>46027</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44615</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45895</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45029</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>46029</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44889</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>46033</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45898</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45898</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>45793</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>46035</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45903</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>46041</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>46041</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>45904</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44671</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>45907</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45434</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45545</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>44897</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44603</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45258</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45602</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45915</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45699</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>46044</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45915</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45915</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44566</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44874</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45798</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45429</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45916</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45916</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45511</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>46051</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44851</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>46050</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45918</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45805</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>46050</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45460</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>45246</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>45257</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45625</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>46055</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45924</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45394</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>46057</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>45924</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>46057</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>46056</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>46056</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>44977</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>46056</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>46056</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44494</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45439</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45930</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45930</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45518</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45922</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45544</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45932</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45572</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>46070</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45938</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45939</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46072</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46072</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45244</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>44526</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>46072</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46072</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>46072</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>46076</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>46077</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45811</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45580</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>46079</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45058</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>46079</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45951</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>46079</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>46079</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45950</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45950</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>46079</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45951</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45951</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45951</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45951</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45950</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45953</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45952</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>46083</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>46083</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46084</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45953</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>45952</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45952</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45953</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45953</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44872</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45092</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45386</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45394</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45954</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44558</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45764</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44826</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>44826</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>46091</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>46092</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>46092</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45965</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>46091</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46091</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>46092</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>46091</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>46092</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45334</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>45971</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>46098</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>45755</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45201</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45520</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45975</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>46105</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>46106</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>45819</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45818</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45819</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>46106</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45981</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45107</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45982</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>45985</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45985</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>46111</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45824</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45822</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>46114</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45822</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44732</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45244</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45982</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>46119</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>44798</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45827</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>46126</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45953</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44721</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>44676</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45861</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45579</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46000</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45831</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>44725</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45210</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45671</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45455</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45455</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45834</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45838</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45839</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45839</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>45190</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>45837</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>45837</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>44798</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45840</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45840</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45840</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45840</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45845</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45847</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45847</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44952</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45849</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45953</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45182</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>44889</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45855</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45761</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45589</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>46024</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44615</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>45859</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45859</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45579</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45927</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>45798</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45859</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45859</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>46139</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>46093</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>45918</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>44952</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45762</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44522</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>46066</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45590</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45622</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45058</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45903</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45614</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>46141</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>46094</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45058</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45187</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45541</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44846</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44854</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45940</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>46057</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44818</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45761</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>44529</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>46147</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45166</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>46147</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45442</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
         <v>45624</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>46150</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>46152</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>45580</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>46150</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>46029</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45733</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45510</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>46029</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45042</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>44732</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45163</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44655</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>46066</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>44531</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45558</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         <v>46160</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>46160</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>45469</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>45915</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44725</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45723</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45877</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46072</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>46150</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>45880</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45880</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45624</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>44880</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>46174</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45092</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45231</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45883</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>46098</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45884</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>46059</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45586</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>46105</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45182</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45621</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45188</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>46095</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>46087</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45058</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45555</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>46191</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>46191</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>46195</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>45182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>46196</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>46202</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46202</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>46202</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45646</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>45441</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>44557</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>44893</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45435</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>46205</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>46212</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>45032</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46259</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>46259</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>46259</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44575</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45188</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46106</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45622</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45058</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45406</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45593</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45043</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45195</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45189</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45987</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45562</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45175</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45250</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45625</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45117</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45579</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>44869</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45435</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>46232</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>46232</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>46275</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>46232</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>46232</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>46275</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>46232</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>46066</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>46041</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47191,7 +47191,7 @@
         <v>45446</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>46188</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>46281</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45386</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>46280</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45103</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45553</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>46281</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>46281</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45579</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45579</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>46240</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>46282</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>44952</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>44530</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>44531</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45079</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>44616</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>46286</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45614</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48691,7 +48691,7 @@
         <v>46289</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>46288</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>46289</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45495</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45407</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>46289</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49144,7 +49144,7 @@
         <v>45344</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>44630</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>46289</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>46248</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45579</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45252</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>46259</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>44869</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>44886</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>46252</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>45656</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>46252</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>46252</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>46295</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
         <v>46091</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45895</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45370</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50415,7 +50415,7 @@
         <v>44557</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>46253</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>46253</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50634,7 +50634,7 @@
         <v>46255</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>44839</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>46254</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>46253</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45148</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45495</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45250</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45104</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>44936</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>44595</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>44872</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>44924</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45595</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45749</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45671</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>44888</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>44530</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>44952</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45209</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>45569</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>44889</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52192,7 +52192,7 @@
         <v>45099</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>44895</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>45560</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45569</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45498</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45033</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45782</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>45783</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45784</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>45784</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45785</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>45789</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53113,7 +53113,7 @@
         <v>44721</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>45114</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>45394</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45041</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45394</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>45041</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>45036</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45733</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53722,7 +53722,7 @@
         <v>45758</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>46083</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>46083</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>46098</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54034,7 +54034,7 @@
         <v>46162</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>46162</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>

--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>254</v>
       </c>
       <c r="U2" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45789</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>46191</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46177</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45793</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45723</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45791</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>45845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>45204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>46120</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45082</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45785</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45215</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45429</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>45786</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>45797</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45895</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45884</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45709</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45786</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45800</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>9</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45804</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45743</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45371</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45764</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45098</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45915</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45791</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45791</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45208</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>45614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44483</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>4</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>45953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45167</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>46092</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>46183</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45329</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45783</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>45786</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45131</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45812</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45812</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45835</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45837</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45671</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45866</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45867</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45561</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45614</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>46148</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>46183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>46196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>46205</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>46177</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45106</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45889</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45548</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45614</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45777</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45786</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44641</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>45785</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45356</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45191</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45302</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45622</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>45797</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45827</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45618</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>45142</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45183</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45187</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>46101</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45867</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45859</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>45751</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45967</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45762</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>46148</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>45889</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45702</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45411</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45119</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44966</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45894</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45785</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45785</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>45790</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45624</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>45791</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45791</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45791</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45548</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45796</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>44641</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45751</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>45112</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45826</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>45951</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45960</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45837</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45837</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45979</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45442</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45579</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45187</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45349</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>46072</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>46072</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>46013</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>46072</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>46092</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>46059</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>46095</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>46205</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>46282</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>1</v>
       </c>
       <c r="U149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V149" s="2" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>46244</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>46302</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>44517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44833</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44557</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44721</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44813</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>44868</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44789</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44782</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44557</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44524</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44491</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>44852</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>44804</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44860</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>44833</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44712</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>44799</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44642</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44642</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44833</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44849</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44854</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44879</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44846</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44887</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>44845</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44511</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44830</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44616</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44895</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>44790</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44641</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45735</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44952</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45188</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45092</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44798</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44872</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45434</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>44936</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45250</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45334</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44869</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44889</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45058</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>44854</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45092</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>44952</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45394</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45103</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45043</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44526</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45545</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>44728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45344</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45656</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45394</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45257</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45446</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45474</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>44725</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45579</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45579</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>45246</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45884</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45190</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>44839</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45884</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45883</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45821</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45107</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45888</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45002</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45058</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45435</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45518</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44531</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45886</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44886</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45201</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44558</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45058</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45469</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45625</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45455</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>45498</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44818</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45895</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45898</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45898</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45621</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44869</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>45629</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45407</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45058</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45058</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>44880</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44732</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45029</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45033</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45439</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>45904</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45903</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44889</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44872</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45907</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44530</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44531</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45782</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45593</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45595</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45915</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>44494</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45915</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45916</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>45783</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45182</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45915</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45784</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45784</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45125</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45916</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45446</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>44721</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44889</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45406</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45785</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45918</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45572</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44575</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45460</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45166</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45786</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>45580</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45558</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45555</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28332,7 +28332,7 @@
         <v>45544</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45789</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45351</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45789</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>44557</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44888</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45924</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45789</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44557</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45924</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45790</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45624</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>44915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>45032</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45187</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45930</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45793</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45930</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>44603</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45699</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44578</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45922</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45602</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45258</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45511</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45932</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>44874</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45148</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44630</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45614</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45798</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45429</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>45579</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44893</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45572</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45579</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>44676</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45560</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45579</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44977</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45386</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45058</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45805</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45386</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45646</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>45938</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45569</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>45580</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32014,7 +32014,7 @@
         <v>45182</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>44608</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44615</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44615</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45939</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45553</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32472,7 +32472,7 @@
         <v>45943</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>44952</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45811</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45117</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45495</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45231</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44732</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>45818</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45950</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45819</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45569</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45579</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45819</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45950</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45822</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45824</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45441</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45822</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45636</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45950</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45625</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45951</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45951</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45435</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>45831</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45952</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45642</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45951</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45951</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45951</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45952</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45952</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45954</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45953</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45953</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45953</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45953</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45834</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45837</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45838</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>45837</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45189</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45610</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>45840</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45840</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44522</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45840</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45839</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>44671</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45965</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45840</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>45839</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45104</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45210</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>44721</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45637</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45455</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45971</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45845</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>45244</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45847</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45749</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45847</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45723</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>45849</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>45975</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45671</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45855</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>45859</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45798</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45859</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45859</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>45859</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45370</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45510</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44851</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>44595</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45764</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>44845</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44846</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>45880</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>44826</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44826</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>45880</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45261</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45981</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>44529</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45877</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45981</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45755</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45495</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45250</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45541</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>46098</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45982</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45586</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45079</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45985</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45985</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>45624</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45175</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45244</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>46105</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45985</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>46106</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>46106</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>46111</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45671</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45982</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>44616</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>44860</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45590</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>45163</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45733</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>46114</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45622</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>45520</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>46119</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>44629</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45953</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>44566</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>46126</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>46000</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45099</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>45861</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>44725</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>46006</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>46006</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>46007</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45614</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>46019</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45985</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45972</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>46019</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>45985</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45916</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45761</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>46023</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>46024</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>46024</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>46027</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45940</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>45645</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44530</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>46029</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>44952</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>46033</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>46139</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44655</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45953</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>46035</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>46066</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43936,7 +43936,7 @@
         <v>45622</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>46041</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>46041</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45195</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>46024</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45252</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45562</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>46044</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>45927</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45589</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>44798</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>45442</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45918</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>46050</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45762</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45579</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46050</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>45903</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45058</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46094</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>46057</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>46051</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>46056</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>46055</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>46056</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>46056</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>46093</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>46056</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>46056</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>46057</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46057</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45761</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46066</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>46147</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>46147</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>46150</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>46150</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>46070</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>46072</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>46072</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>46072</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>46072</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>46072</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>46076</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>46077</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>46079</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>46079</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>46079</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>46079</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>46079</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>46029</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46083</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>46152</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>46083</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45042</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>46084</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>46029</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>46091</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>46160</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>46160</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>46091</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>46091</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>46091</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>46092</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>46066</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>46092</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>46092</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>46092</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45915</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>46150</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>46072</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>46174</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>46098</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>46105</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>46059</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>46087</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>46095</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>46191</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>46191</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>46195</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>46196</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>46202</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46202</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>46202</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>46205</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>46212</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>46106</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45987</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>46275</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>46232</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>46232</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46232</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>46275</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>46232</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>46232</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>46188</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>46280</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46066</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>46240</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>46281</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>46281</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>46282</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>46281</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>46286</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>46288</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>46289</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>46289</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>46289</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>46289</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>46248</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>46253</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>46253</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
         <v>46253</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>46252</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>46295</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46252</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>46252</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52582,7 +52582,7 @@
         <v>46300</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>46091</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>46254</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>46300</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>46255</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>46300</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>46259</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>46302</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>46041</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53254,7 +53254,7 @@
         <v>46259</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53332,7 +53332,7 @@
         <v>46259</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>46259</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>46303</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>45895</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>46303</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>46304</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>46304</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>45114</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45394</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>45041</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54082,7 +54082,7 @@
         <v>45394</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54160,7 +54160,7 @@
         <v>45041</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45036</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45733</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54389,7 +54389,7 @@
         <v>45758</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>46083</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>46083</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>46098</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>46162</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>46162</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>

--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45789</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>46191</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46177</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45793</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45723</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45791</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>45845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>45204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>46120</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45082</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45785</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45215</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45429</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>45786</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>45797</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45895</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45884</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45709</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45786</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45800</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45804</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45743</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45229</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45371</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45764</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45098</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45915</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45791</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45791</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45208</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>45614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44483</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45953</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>45953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45167</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>46092</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>46183</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45329</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45783</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>45786</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45131</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45812</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45812</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45835</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45837</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45671</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45866</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>45867</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45561</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45614</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>46148</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>46183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>46196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>46205</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>46177</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45106</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45889</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45548</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45614</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45777</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45786</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44641</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>45785</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45356</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45191</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45302</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45622</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>45797</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45827</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45618</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>45142</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45183</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45187</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>46101</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45867</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45859</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>45751</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45967</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45762</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>46148</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>45889</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45702</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45411</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45119</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44966</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45894</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45785</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45785</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>45790</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45624</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>45791</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45791</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45791</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45548</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45796</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>44641</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45751</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>45112</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45826</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>45951</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45960</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45837</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45837</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45979</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45442</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45579</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45187</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45349</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>46072</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>46072</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>46013</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>46072</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>46092</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>46059</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>46095</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>46205</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>46282</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>46244</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>46302</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>44517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44833</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44557</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44721</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44813</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>44868</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44789</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44782</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44557</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44524</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44491</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>44852</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>44804</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44860</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>44833</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44712</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>44799</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44642</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44642</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44833</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44849</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44854</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44879</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44846</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44887</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>44845</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44511</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44830</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44616</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44895</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>44790</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44641</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45735</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44952</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45188</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45092</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44798</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44872</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45434</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>44936</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45209</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45250</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45334</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44869</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44889</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45058</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>44854</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45092</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>44952</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45394</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45103</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45043</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44526</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45545</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>44728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45344</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45656</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45394</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45257</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45446</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45474</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>44725</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45579</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45579</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>45246</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45884</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45190</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>44839</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45884</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45883</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45821</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45107</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45888</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45002</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45058</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45435</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45518</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44531</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45886</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44886</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45201</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44558</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45058</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45469</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45625</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45455</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>45498</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44818</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45895</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45898</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45898</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45621</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44869</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>45629</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45407</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45058</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45058</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>44880</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44732</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45029</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45033</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45439</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>45904</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45903</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44889</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44872</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45907</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44530</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44531</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45782</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45593</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45595</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45915</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>44494</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45915</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45916</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>45783</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45182</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45915</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45784</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45784</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45125</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45916</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45446</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>44721</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44889</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45406</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45785</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45918</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45572</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44575</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45460</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45166</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45786</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>45580</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45558</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45555</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28332,7 +28332,7 @@
         <v>45544</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45789</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45351</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45789</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>44557</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>44888</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45924</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45789</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44557</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45924</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45790</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45624</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>44915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>45032</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45187</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45930</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45793</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45930</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>44603</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45699</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44578</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45922</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45602</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45258</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45511</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45932</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>44874</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45148</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44630</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45614</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45798</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45429</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>45579</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44893</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45572</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45579</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>44676</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45560</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45579</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44977</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45386</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45058</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45805</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45386</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45646</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>45938</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45569</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>45580</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32014,7 +32014,7 @@
         <v>45182</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>44608</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44615</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44615</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45939</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45553</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32472,7 +32472,7 @@
         <v>45943</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>44952</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45811</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45117</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45495</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45231</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44732</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>45818</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45950</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45819</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45569</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45579</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45819</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45950</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45822</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45824</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45441</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45822</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45636</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45950</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45625</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45951</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45951</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45435</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>45831</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45952</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45642</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45951</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45951</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45951</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45952</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45952</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45954</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45953</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45953</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45953</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45953</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45834</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45837</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45838</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>45837</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45189</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45610</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>45840</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45840</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44522</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45840</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45839</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>44671</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45965</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45840</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>45839</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45104</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45210</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>44721</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45637</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45455</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45971</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45845</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>45244</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45847</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45749</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45847</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45723</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>45849</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>45975</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45671</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45855</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>45859</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45798</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45859</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45859</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>45859</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45370</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45510</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44851</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>44595</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45764</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>44845</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44846</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>45880</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>44826</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44826</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>45880</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45261</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45981</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>44529</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45877</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45981</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45755</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45495</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45250</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45541</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>46098</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45982</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45586</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45079</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45985</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45985</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>45624</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45175</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45244</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>46105</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45985</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>46106</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>46106</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>46111</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45671</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45982</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>44616</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>44860</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45590</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>45163</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45733</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>46114</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45622</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>45520</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>46119</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>44629</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45953</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>44566</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>46126</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>46000</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45099</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>45861</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>44725</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>46006</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>46006</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>46007</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45614</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>46019</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45985</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45972</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>46019</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>45985</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45916</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45761</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>46023</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>46024</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>46024</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>46027</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45940</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>45645</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44530</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>46029</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>44952</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>46033</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>46139</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44655</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45953</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>46035</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>46066</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43936,7 +43936,7 @@
         <v>45622</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>46041</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>46041</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45195</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>46024</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45252</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45562</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>46044</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>45927</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45589</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>44798</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>45442</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45918</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>46050</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45762</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45579</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46050</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>45903</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45058</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46094</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>46057</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>46051</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>46056</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>46055</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>46056</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>46056</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>46093</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>46056</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>46056</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>46057</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46057</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45761</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46066</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>46147</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>46147</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>46150</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>46150</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>46070</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>46072</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>46072</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>46072</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>46072</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>46072</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>46076</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>46077</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>46079</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>46079</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>46079</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>46079</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>46079</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>46029</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46083</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>46152</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>46083</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45042</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>46084</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>46029</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>46091</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>46160</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>46160</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>46091</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>46091</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>46091</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>46092</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>46066</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>46092</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>46092</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>46092</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45915</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>46150</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>46072</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>46174</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>46098</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>46105</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>46059</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>46087</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>46095</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>46191</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>46191</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>46195</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>46196</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>46202</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46202</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>46202</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>46205</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>46212</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>46106</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45987</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>46275</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>46232</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>46232</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46232</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>46275</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>46232</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>46232</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>46188</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>46280</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46066</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>46240</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>46281</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>46281</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>46282</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>46281</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>46286</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>46288</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>46289</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>46289</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>46289</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>46289</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>46248</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>46253</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>46253</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
         <v>46253</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>46252</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>46295</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46252</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>46252</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52582,7 +52582,7 @@
         <v>46300</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>46091</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>46254</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>46300</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>46255</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>46300</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>46259</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>46302</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>46041</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53254,7 +53254,7 @@
         <v>46259</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53332,7 +53332,7 @@
         <v>46259</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>46259</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>46303</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>45895</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>46303</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>46304</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>46304</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>45114</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45394</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>45041</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54082,7 +54082,7 @@
         <v>45394</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54160,7 +54160,7 @@
         <v>45041</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45036</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45733</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54389,7 +54389,7 @@
         <v>45758</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>46083</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>46083</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>46098</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>46162</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>46162</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>

--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46191</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46177</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45793</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45723</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45791</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>45845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45082</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45924</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45785</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45895</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45429</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45786</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45797</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45884</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45709</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45786</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45800</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45371</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>45764</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45804</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45167</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45098</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45915</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45953</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45953</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45208</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>46183</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>45785</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45614</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>46148</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>46183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>46196</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>45867</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45866</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45561</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>46177</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45783</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45786</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45131</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45812</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45812</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45835</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45751</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45762</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>45889</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45898</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>46148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45622</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45187</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45191</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45967</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45889</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45548</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>46101</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45866</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>45859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45867</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45618</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45106</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45142</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45614</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45777</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45785</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45786</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45356</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44641</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45797</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45827</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>46083</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46093</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>46309</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45349</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45702</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45894</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44966</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45951</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>46013</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45187</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>45960</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45979</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45751</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45624</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>46059</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45112</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45442</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>46072</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>46072</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>46072</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>46095</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46092</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45446</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45579</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>46205</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44641</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>46282</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>45411</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>46244</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45785</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45785</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45789</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45789</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46302</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45791</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45790</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45791</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45791</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45796</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45548</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45826</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45837</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45837</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>44517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>44557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44833</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>44557</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>44721</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44813</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>44868</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>44789</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>44782</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>44524</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>44557</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>44491</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>44852</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44879</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>44511</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>44712</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44849</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44846</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44616</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>44804</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>44799</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>44854</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44887</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>44845</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44860</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44833</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44642</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>44642</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44833</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>44641</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44790</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45610</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44578</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45187</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45261</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45474</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>44728</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45351</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44629</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45642</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>45125</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45629</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45058</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45058</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44608</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44860</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45636</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>44845</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45645</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45637</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45002</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45579</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45735</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>44615</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45029</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>44889</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>44671</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45545</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44566</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45434</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44851</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45460</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45246</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45257</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45439</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44977</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45394</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44494</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45544</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44526</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45244</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>45058</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>44872</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>45092</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45386</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45394</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44558</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45764</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44826</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>44826</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45334</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45520</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45755</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45201</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45107</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45518</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45884</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44732</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45244</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45953</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>44798</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>44721</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45821</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>44676</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45888</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45761</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45589</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45579</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45895</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>46024</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45884</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>45886</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45210</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45927</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>46139</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>46093</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45918</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44952</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>46066</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45622</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45058</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45903</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45614</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>45898</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>46094</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45898</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45671</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45903</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>45455</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>45455</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>45904</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45940</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46057</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45907</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45190</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45915</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>45915</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45916</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45761</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45916</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45918</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>46147</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>46147</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>44952</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45924</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45924</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45182</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45930</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45930</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45922</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>46150</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>46152</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45932</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>44889</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45938</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45939</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>46150</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45943</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>44615</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45579</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>46029</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45762</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>44522</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45951</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45950</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45950</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45951</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45951</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>45951</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>45951</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45950</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45953</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>46029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>45590</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45952</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45042</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45953</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>45952</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45952</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45953</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45953</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45058</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45954</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>46066</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45541</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44846</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45965</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44854</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>46160</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46160</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45971</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>44818</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44529</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45166</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45442</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45975</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45624</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45981</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45981</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45580</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45982</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45985</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45985</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45733</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45510</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45985</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44732</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>46072</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45163</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>44655</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>46150</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44531</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45982</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45558</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45469</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45953</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>44725</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45723</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46000</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>46006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>46006</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45624</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>46007</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>46174</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44880</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45092</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45231</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45586</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>46019</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45972</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>45985</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45985</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>46019</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45916</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>46023</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>46024</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>46024</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>46027</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45182</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45621</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>45188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>46029</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>46033</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46098</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>46035</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>46041</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>46041</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>46059</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>46105</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>46044</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45058</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45555</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>46051</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>46050</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>46050</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45182</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>46055</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>46057</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>46057</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>46056</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>46056</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>46056</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>46056</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>46056</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>46066</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>46070</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46072</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46072</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46072</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>46072</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>46072</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>46076</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45646</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>46077</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>45441</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>44557</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>46079</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>46079</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>46079</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>44893</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>46079</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>46079</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45435</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>46083</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>46083</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>46084</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46095</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>46087</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>46091</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>46092</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>46092</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>46091</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>46091</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>46092</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>46091</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>46092</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>46191</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45032</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46191</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>46195</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>46098</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>44575</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45188</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45622</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>46196</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>45058</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>46105</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>45406</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>45593</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>46106</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>45043</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>46106</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45195</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45189</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>46111</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>46114</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45562</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45175</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>46119</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>45250</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>46202</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>46126</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>45625</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>46202</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45117</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45579</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>46202</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>45861</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>44869</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>44725</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45435</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45446</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45386</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45103</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>45553</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44798</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45579</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>45579</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>46205</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>44952</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42841,7 +42841,7 @@
         <v>46212</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>44530</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>44531</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>45079</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>44616</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45614</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46106</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45495</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45407</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45987</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>45344</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>44630</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>46232</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>46232</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>45579</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>46275</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>46232</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>46232</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45252</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>46275</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>46232</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>44869</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>44886</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>46066</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45656</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>46188</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>46281</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>46280</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>46281</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>46281</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>46240</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45370</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>46282</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>44557</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>44839</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45148</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>46286</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>45495</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45250</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45104</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>44936</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>46289</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>44595</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>46288</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>46289</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>46289</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>44872</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46327,7 +46327,7 @@
         <v>46289</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>44924</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45595</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>46248</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45749</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>45671</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44888</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>44530</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>44952</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46252</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>45209</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>46252</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45569</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44889</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46252</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>46295</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47520,7 +47520,7 @@
         <v>45099</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>44895</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45560</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45569</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>46091</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45498</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>46253</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>46253</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>46254</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48197,7 +48197,7 @@
         <v>46253</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>46255</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45033</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>46300</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48499,7 +48499,7 @@
         <v>46259</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
         <v>45782</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45783</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48728,7 +48728,7 @@
         <v>45784</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>45784</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45785</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>46300</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>46300</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45789</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>44721</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49254,7 +49254,7 @@
         <v>46303</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45789</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>46259</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45446</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45572</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45789</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45786</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>44915</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>46303</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>46259</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>45790</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>46259</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>46302</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45793</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>44603</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>45258</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>45602</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45699</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>46304</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>46304</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>44874</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45798</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45429</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>46307</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>45511</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>45895</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45805</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>46309</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45811</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45580</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45819</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45818</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45819</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45824</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>45822</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45822</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>45827</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>46289</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>46041</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45831</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45834</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45838</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45839</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45839</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>45837</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45837</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         <v>45840</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52815,7 +52815,7 @@
         <v>45840</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52888,7 +52888,7 @@
         <v>45840</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52961,7 +52961,7 @@
         <v>45840</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>45845</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45847</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45847</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53263,7 +53263,7 @@
         <v>45849</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>45855</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53414,7 +53414,7 @@
         <v>45859</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53487,7 +53487,7 @@
         <v>45859</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53560,7 +53560,7 @@
         <v>45798</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45859</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45859</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53779,7 +53779,7 @@
         <v>45877</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53852,7 +53852,7 @@
         <v>45880</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53925,7 +53925,7 @@
         <v>45880</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45883</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45114</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>45394</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>45041</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45394</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45041</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54456,7 +54456,7 @@
         <v>45036</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54529,7 +54529,7 @@
         <v>45733</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>45758</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>46083</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54763,7 +54763,7 @@
         <v>46083</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54841,7 +54841,7 @@
         <v>46098</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>46162</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>46162</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>

--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46191</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46177</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45793</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45723</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45791</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>45845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45082</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45924</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45940</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45785</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45895</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45429</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45786</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45797</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45884</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45709</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45786</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45800</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45371</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>45764</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45791</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45804</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45167</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45098</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45915</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45953</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45953</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45208</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>46183</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>45785</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45614</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>46148</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>46183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>46196</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>45867</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45866</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45561</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>46177</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45783</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45786</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45131</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45812</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45812</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45835</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45751</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45762</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>45889</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45898</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>46148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45622</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45187</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45191</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45967</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45889</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45548</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>46101</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45866</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>45859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45867</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45618</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45106</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45142</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45614</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45777</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45785</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45786</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45356</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44641</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45797</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45827</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>46083</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46093</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>46309</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45349</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45702</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45894</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44966</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45951</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>46013</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45187</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>45960</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45979</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45751</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45624</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>46059</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45112</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45442</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>46072</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>46072</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>46072</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>46095</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46092</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45446</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45579</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>46205</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44641</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>46282</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>45411</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>46244</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45785</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45785</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45789</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45789</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46302</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45791</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45790</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45791</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45791</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45796</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45548</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45826</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45837</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45837</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>44517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>44557</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44833</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>44557</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>44721</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>44813</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>44868</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>44789</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>44782</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>44524</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>44557</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>44491</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>44852</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44879</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>44511</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>44712</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44849</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44846</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44616</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>44804</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>44799</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>44854</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44887</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>44845</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44860</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44833</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44642</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>44642</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44833</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>44641</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44790</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45610</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44578</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45187</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45261</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45474</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>44728</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45351</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44629</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45642</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>45125</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45629</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45058</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45058</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44608</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44860</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45636</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>44845</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45645</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45637</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45002</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45579</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45735</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>44615</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45029</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>44889</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>44671</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45545</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44566</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45434</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44851</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45460</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45246</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45257</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45439</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44977</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45394</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44494</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45544</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44526</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45244</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>45058</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>44872</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>45092</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45386</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45394</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44558</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45764</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44826</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>44826</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45334</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45520</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45755</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45201</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45107</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45518</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45884</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44732</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45244</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45953</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>44798</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>44721</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45821</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>44676</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45888</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45761</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45589</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45579</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45895</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>46024</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45884</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>45886</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45210</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45927</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>46139</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>46093</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45918</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44952</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>46066</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45622</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45058</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45903</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45614</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>45898</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>46094</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45898</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45671</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45903</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>45455</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>45455</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>45904</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45940</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46057</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45907</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45190</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45915</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>45915</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45916</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45761</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45916</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45918</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>46147</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>46147</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>44952</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45924</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45924</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45182</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45930</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45930</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45922</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>46150</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>46152</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45932</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>44889</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45938</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45939</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>46150</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45943</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>44615</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45579</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>46029</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45762</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>44522</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45951</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45950</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45950</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45951</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45951</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>45951</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>45951</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45950</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45953</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>46029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>45590</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45952</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45042</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45953</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>45952</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45952</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45953</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45953</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45058</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45954</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>46066</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45541</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44846</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45965</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44854</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>46160</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46160</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45971</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>44818</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44529</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45166</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45442</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45975</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45624</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45981</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45981</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45580</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45982</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45985</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45985</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45733</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45510</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45985</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44732</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>46072</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45163</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>44655</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>46150</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44531</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45982</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45558</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45469</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45953</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>44725</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45723</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46000</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>46006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>46006</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45624</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>46007</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>46174</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44880</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45092</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45231</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45586</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>46019</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45972</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>45985</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45985</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>46019</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45916</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>46023</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>46024</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>46024</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>46027</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45182</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45621</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>45188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>46029</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>46033</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46098</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>46035</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>46041</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>46041</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>46059</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>46105</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>46044</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45058</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45555</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>46051</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>46050</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>46050</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45182</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>46055</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>46057</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>46057</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>46056</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>46056</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>46056</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>46056</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>46056</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>46066</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>46070</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46072</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46072</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46072</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>46072</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>46072</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>46076</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45646</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>46077</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>45441</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>44557</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>46079</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>46079</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>46079</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>44893</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>46079</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>46079</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45435</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>46083</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>46083</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>46084</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46095</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>46087</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>46091</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>46092</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>46092</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>46091</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>46091</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>46092</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>46091</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>46092</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>46191</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45032</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46191</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>46195</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>46098</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>44575</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45188</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45622</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>46196</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>45058</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>46105</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>45406</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>45593</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>46106</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>45043</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>46106</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45195</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45189</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>46111</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>46114</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45562</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45175</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>46119</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>45250</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>46202</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>46126</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>45625</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>46202</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45117</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45579</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>46202</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>45861</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>44869</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>44725</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45435</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45446</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45386</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45103</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>45553</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44798</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45579</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>45579</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>46205</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>44952</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42841,7 +42841,7 @@
         <v>46212</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>44530</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>44531</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>45079</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>44616</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45614</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46106</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45495</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45407</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45987</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>45344</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>44630</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>46232</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>46232</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>45579</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>46275</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>46232</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>46232</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45252</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>46275</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>46232</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>44869</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>44886</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>46066</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45656</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>46188</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>46281</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>46280</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>46281</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>46281</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>46240</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45370</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>46282</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>44557</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>44839</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45148</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>46286</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>45495</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45250</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45104</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>44936</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>46289</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>44595</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>46288</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>46289</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>46289</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>44872</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46327,7 +46327,7 @@
         <v>46289</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>44924</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45595</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>46248</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45749</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>45671</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44888</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>44530</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>44952</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46252</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>45209</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>46252</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45569</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>44889</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46252</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>46295</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47520,7 +47520,7 @@
         <v>45099</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>44895</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45560</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45569</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>46091</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45498</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>46253</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>46253</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>46254</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48197,7 +48197,7 @@
         <v>46253</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>46255</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45033</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>46300</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48499,7 +48499,7 @@
         <v>46259</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
         <v>45782</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45783</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48728,7 +48728,7 @@
         <v>45784</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>45784</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45785</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>46300</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>46300</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45789</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>44721</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49254,7 +49254,7 @@
         <v>46303</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45789</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>46259</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45446</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45572</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45789</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45786</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>44915</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>46303</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>46259</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>45790</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>46259</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>46302</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45793</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>44603</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>45258</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>45602</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45699</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>46304</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>46304</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>44874</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45798</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45429</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>46307</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>45511</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>45895</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45805</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>46309</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45811</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45580</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45819</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45818</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45819</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45824</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>45822</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45822</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>45827</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>46289</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>46041</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45831</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45834</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45838</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45839</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45839</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>45837</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45837</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         <v>45840</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52815,7 +52815,7 @@
         <v>45840</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52888,7 +52888,7 @@
         <v>45840</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52961,7 +52961,7 @@
         <v>45840</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>45845</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45847</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45847</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53263,7 +53263,7 @@
         <v>45849</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>45855</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53414,7 +53414,7 @@
         <v>45859</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53487,7 +53487,7 @@
         <v>45859</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53560,7 +53560,7 @@
         <v>45798</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45859</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45859</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53779,7 +53779,7 @@
         <v>45877</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53852,7 +53852,7 @@
         <v>45880</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53925,7 +53925,7 @@
         <v>45880</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45883</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45114</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>45394</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>45041</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45394</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45041</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54456,7 +54456,7 @@
         <v>45036</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54529,7 +54529,7 @@
         <v>45733</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>45758</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>46083</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54763,7 +54763,7 @@
         <v>46083</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54841,7 +54841,7 @@
         <v>46098</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>46162</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>46162</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>

--- a/Översikt TIMRÅ.xlsx
+++ b/Översikt TIMRÅ.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>45924</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>45323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45239</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46191</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>44809</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>46177</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>45793</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45723</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45791</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>45845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45924</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45924</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45785</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>45082</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45429</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>45786</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>45797</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45895</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45884</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45709</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45786</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45797</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45800</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45804</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45764</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45229</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45371</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46083</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45915</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>46183</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45953</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45953</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45785</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45791</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>45791</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>45614</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>45098</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45208</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45167</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45898</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>46183</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>46196</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>46205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>46177</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45783</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45786</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45131</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45812</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>45812</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>45835</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45837</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45866</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45614</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>46148</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45671</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45329</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45561</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45889</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44830</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45106</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45548</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45777</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45786</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44641</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45785</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45967</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45356</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>45302</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45797</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45889</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>46101</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>45867</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45859</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45866</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45762</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>45191</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>46148</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>45618</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45142</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45183</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>45187</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>45751</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45622</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>46083</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>46093</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>46309</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45702</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45894</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45579</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45187</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45349</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>46059</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45951</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45411</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45960</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>46095</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45119</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45979</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>46205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45785</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45785</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>46282</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45790</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45789</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45789</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45791</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45791</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>46244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45791</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45548</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45796</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44966</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>46072</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>46072</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46072</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45826</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45837</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45837</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>46092</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>46302</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45624</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45446</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>46013</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44641</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>45646</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45751</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45112</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45442</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44517</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>44557</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44833</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>44557</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>44721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>44813</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44868</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>44789</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44782</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>44557</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>44524</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>44607</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>44852</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44879</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>44511</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44712</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44849</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44846</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>44616</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>44804</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>44799</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>44854</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>44887</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>44845</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44860</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44833</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44642</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44642</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44833</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45883</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44790</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44641</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45821</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45886</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>44798</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45334</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45058</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45884</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45895</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45043</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45898</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45898</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45884</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45903</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>45907</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>46066</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>45645</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44530</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45915</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45915</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>45915</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45916</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45916</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>44655</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45918</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>46150</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>46072</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45924</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45924</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45195</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45252</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>45562</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45930</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45930</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45092</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45922</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>45932</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45442</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>46174</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45434</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45762</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45579</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>44952</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>45939</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45943</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45250</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>46098</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44854</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>46105</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>44952</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>45188</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>46059</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>45545</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45950</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>44936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45951</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45951</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>44889</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45952</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45951</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>45951</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45951</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45952</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45952</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45954</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45953</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45953</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45953</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45953</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>46087</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>46095</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44728</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45188</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45965</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46191</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>46191</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45394</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46195</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45971</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45474</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44725</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45579</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45579</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>46196</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>45246</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>45190</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45975</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45002</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45058</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46202</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46202</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45981</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46202</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45981</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>46205</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45201</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45982</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>45058</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45985</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45985</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44924</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45625</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45985</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>44818</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45621</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45446</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45629</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45407</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>45058</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>45058</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>45982</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>46212</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>45953</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44839</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>46000</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45987</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45782</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>46006</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>46006</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45783</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45784</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45784</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>46232</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>46232</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>46007</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45446</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>46232</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>44721</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>46232</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>46232</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45785</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45572</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>46188</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>46280</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45786</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>46066</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>46019</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30846,7 +30846,7 @@
         <v>45985</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45972</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45789</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>46019</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45985</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45789</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31304,7 +31304,7 @@
         <v>45916</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>46240</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>46281</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>46281</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>46023</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>46024</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>46024</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>46027</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45789</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45790</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>46281</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44915</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>46029</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>46033</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>46035</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45793</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>44603</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45699</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>46286</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45435</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45602</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>46288</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>46041</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45258</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>46041</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45511</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>44874</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45798</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>46044</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45429</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>46050</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45518</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>46050</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46289</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46289</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>46051</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44531</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46056</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>46055</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45805</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>46056</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46056</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>46289</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>46056</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>46056</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45580</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>46057</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>46057</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>44886</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45811</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46066</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45818</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>46248</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46070</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45819</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>46072</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>46072</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46253</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46072</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45819</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>46072</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>46072</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46253</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46076</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>46253</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45822</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46077</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>45824</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>46252</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>45822</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>46079</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>46079</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>46295</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>46079</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>46079</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>46079</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45827</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>46083</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>46252</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>46252</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>46083</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>46084</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45831</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>46300</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>46091</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45834</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>46091</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>45837</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>46254</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>45838</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45837</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>46300</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>46091</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46091</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>46091</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46092</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45840</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45840</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45840</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>46092</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>46092</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>46092</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45839</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>45840</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45469</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45839</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46098</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45845</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>46255</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>46300</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45498</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>46259</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45847</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>44869</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>45847</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>46302</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>46105</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45849</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>46106</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>46259</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>46106</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45855</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>46111</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>46259</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>46259</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45859</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>45798</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45859</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>45859</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41072,7 +41072,7 @@
         <v>45859</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>46303</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>44880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>46303</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>46114</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>46119</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>46304</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>46304</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45033</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>45439</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>46126</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>45880</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45880</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45877</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>45861</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>44889</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44725</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44872</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>44897</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>44530</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>44531</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>46307</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>44889</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>45406</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45895</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>46309</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45614</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>45761</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>45940</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>46041</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45555</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45544</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>45351</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>44952</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>44557</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>44888</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45182</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>46139</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>45624</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>46289</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>45953</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>46066</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>45032</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45622</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>46024</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45927</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45589</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>44798</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45918</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>46318</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>44630</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>45614</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>46275</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45903</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45579</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45058</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>46094</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>46057</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45411,7 +45411,7 @@
         <v>44893</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>46093</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>46317</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45572</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>44676</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45560</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>46275</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>46317</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45761</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45579</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>44977</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45386</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46147</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>46147</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>46150</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>46150</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45569</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45182</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45553</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>46029</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46911,7 +46911,7 @@
         <v>44952</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>46152</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45042</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>46029</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>46160</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>46160</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>45569</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45579</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>45636</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>45625</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45642</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45610</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>44522</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45104</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45210</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45637</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45455</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>45723</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45510</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>44851</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>45764</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>44845</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>44846</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>44529</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45755</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45586</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45079</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45624</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45175</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>44616</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49171,7 +49171,7 @@
         <v>44860</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45590</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45163</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>44895</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45735</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>44872</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45209</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>44869</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45092</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45394</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45103</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>44526</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45344</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>45656</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50213,7 +50213,7 @@
         <v>45257</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50291,7 +50291,7 @@
         <v>45107</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>44558</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45455</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>44732</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>45029</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45593</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>45595</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>44494</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45182</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>45125</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>44575</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>45460</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45166</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45580</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>45558</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>44557</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>45187</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>44578</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>45148</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45579</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45058</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45386</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
         <v>44608</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>44615</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52083,7 +52083,7 @@
         <v>44615</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52156,7 +52156,7 @@
         <v>45117</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52229,7 +52229,7 @@
         <v>45495</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         <v>45231</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>44732</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>45441</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>45435</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45189</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>44671</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>44721</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>45244</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52911,7 +52911,7 @@
         <v>45749</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52984,7 +52984,7 @@
         <v>45671</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53057,7 +53057,7 @@
         <v>45370</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>44595</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53208,7 +53208,7 @@
         <v>44826</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53281,7 +53281,7 @@
         <v>44826</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45261</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>45495</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>45250</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>45541</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45244</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>45671</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45733</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>45622</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45520</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>44629</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>44566</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45099</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45114</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>45394</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54406,7 +54406,7 @@
         <v>45041</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54484,7 +54484,7 @@
         <v>45394</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54562,7 +54562,7 @@
         <v>45041</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54640,7 +54640,7 @@
         <v>45036</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54713,7 +54713,7 @@
         <v>45733</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>45758</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>46083</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>46083</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>46098</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>46162</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>46162</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
